--- a/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78DE2CE3-8DBC-4C6B-9766-44567EE7B165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2C7644C-2894-4662-8E25-4E5BABC3DC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2C7644C-2894-4662-8E25-4E5BABC3DC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{199EEB8B-3C69-402B-8E4A-D8EF27465C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="151">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>at grid node - w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
   </si>
   <si>
     <t>w899264357-380_SAU</t>
@@ -899,7 +902,7 @@
         <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="G11" t="s">
         <v>111</v>
@@ -917,10 +920,10 @@
         <v>111</v>
       </c>
       <c r="M11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O11" t="s">
         <v>105</v>
@@ -931,22 +934,22 @@
         <v>111</v>
       </c>
       <c r="C12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" t="s">
         <v>114</v>
       </c>
-      <c r="D12" t="s">
+      <c r="G12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" t="s">
         <v>115</v>
       </c>
-      <c r="E12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" t="s">
-        <v>114</v>
-      </c>
       <c r="I12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J12" t="s">
         <v>102</v>
@@ -955,10 +958,10 @@
         <v>111</v>
       </c>
       <c r="M12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O12" t="s">
         <v>105</v>
@@ -969,22 +972,22 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" t="s">
         <v>117</v>
       </c>
-      <c r="E13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" t="s">
-        <v>116</v>
-      </c>
       <c r="I13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J13" t="s">
         <v>102</v>
@@ -993,10 +996,10 @@
         <v>111</v>
       </c>
       <c r="M13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O13" t="s">
         <v>105</v>
@@ -1007,22 +1010,22 @@
         <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" t="s">
         <v>119</v>
       </c>
-      <c r="E14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" t="s">
-        <v>118</v>
-      </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J14" t="s">
         <v>102</v>
@@ -1031,10 +1034,10 @@
         <v>111</v>
       </c>
       <c r="M14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O14" t="s">
         <v>105</v>
@@ -1045,22 +1048,22 @@
         <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" t="s">
         <v>121</v>
       </c>
-      <c r="E15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" t="s">
-        <v>120</v>
-      </c>
       <c r="I15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" t="s">
         <v>102</v>
@@ -1069,10 +1072,10 @@
         <v>111</v>
       </c>
       <c r="M15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O15" t="s">
         <v>105</v>
@@ -1083,22 +1086,22 @@
         <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
         <v>111</v>
       </c>
       <c r="H16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J16" t="s">
         <v>102</v>
@@ -1107,10 +1110,10 @@
         <v>111</v>
       </c>
       <c r="M16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O16" t="s">
         <v>105</v>
@@ -1121,22 +1124,22 @@
         <v>111</v>
       </c>
       <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" t="s">
+        <v>123</v>
+      </c>
+      <c r="I17" t="s">
         <v>124</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" t="s">
-        <v>123</v>
       </c>
       <c r="J17" t="s">
         <v>102</v>
@@ -1145,10 +1148,10 @@
         <v>111</v>
       </c>
       <c r="M17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O17" t="s">
         <v>105</v>
@@ -1159,22 +1162,22 @@
         <v>111</v>
       </c>
       <c r="C18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" t="s">
         <v>126</v>
-      </c>
-      <c r="D18" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" t="s">
-        <v>124</v>
-      </c>
-      <c r="I18" t="s">
-        <v>125</v>
       </c>
       <c r="J18" t="s">
         <v>102</v>
@@ -1183,10 +1186,10 @@
         <v>111</v>
       </c>
       <c r="M18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O18" t="s">
         <v>105</v>
@@ -1197,22 +1200,22 @@
         <v>111</v>
       </c>
       <c r="C19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" t="s">
+        <v>127</v>
+      </c>
+      <c r="I19" t="s">
         <v>128</v>
-      </c>
-      <c r="D19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" t="s">
-        <v>127</v>
       </c>
       <c r="J19" t="s">
         <v>102</v>
@@ -1247,10 +1250,10 @@
         <v>111</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" t="s">
         <v>102</v>
@@ -1259,10 +1262,10 @@
         <v>111</v>
       </c>
       <c r="M20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O20" t="s">
         <v>105</v>
@@ -1285,10 +1288,10 @@
         <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J21" t="s">
         <v>102</v>
@@ -1297,10 +1300,10 @@
         <v>111</v>
       </c>
       <c r="M21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O21" t="s">
         <v>105</v>
@@ -1323,10 +1326,10 @@
         <v>111</v>
       </c>
       <c r="H22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J22" t="s">
         <v>102</v>
@@ -1335,10 +1338,10 @@
         <v>111</v>
       </c>
       <c r="M22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O22" t="s">
         <v>105</v>
@@ -1361,10 +1364,10 @@
         <v>111</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J23" t="s">
         <v>102</v>
@@ -1373,10 +1376,10 @@
         <v>111</v>
       </c>
       <c r="M23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O23" t="s">
         <v>105</v>
@@ -1399,10 +1402,10 @@
         <v>111</v>
       </c>
       <c r="H24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J24" t="s">
         <v>102</v>
@@ -1411,10 +1414,10 @@
         <v>111</v>
       </c>
       <c r="M24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O24" t="s">
         <v>105</v>
@@ -1437,10 +1440,10 @@
         <v>111</v>
       </c>
       <c r="H25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J25" t="s">
         <v>102</v>
@@ -1449,10 +1452,10 @@
         <v>111</v>
       </c>
       <c r="M25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O25" t="s">
         <v>105</v>
@@ -1475,10 +1478,10 @@
         <v>111</v>
       </c>
       <c r="M26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O26" t="s">
         <v>105</v>
@@ -1489,10 +1492,10 @@
         <v>111</v>
       </c>
       <c r="M27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O27" t="s">
         <v>105</v>
@@ -1503,10 +1506,10 @@
         <v>111</v>
       </c>
       <c r="M28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O28" t="s">
         <v>105</v>

--- a/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{199EEB8B-3C69-402B-8E4A-D8EF27465C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3D84277-0CC4-4C2B-867B-0524A051EAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
